--- a/docs/oc-top-proveedores/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-proveedores/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="adquisicion-de-v top prov" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="adquisicion-de-v top prov" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -9962,7 +9962,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10393,7 +10393,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10504,7 +10504,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10565,7 +10565,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10885,7 +10885,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11244,7 +11244,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -12045,7 +12045,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -12293,7 +12293,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12354,7 +12354,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12415,7 +12415,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12720,7 +12720,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12842,7 +12842,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13029,7 +13029,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13090,7 +13090,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13151,7 +13151,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13403,7 +13403,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -13712,7 +13712,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13834,7 +13834,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13895,7 +13895,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14021,7 +14021,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14204,7 +14204,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14265,7 +14265,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14696,7 +14696,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14944,7 +14944,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15188,7 +15188,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15253,7 +15253,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15314,7 +15314,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15497,7 +15497,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15619,7 +15619,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15680,7 +15680,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15695,7 +15695,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -15745,7 +15745,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -15810,7 +15810,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15871,7 +15871,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15932,7 +15932,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16298,7 +16298,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16729,7 +16729,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16790,7 +16790,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16912,7 +16912,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17095,7 +17095,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17217,7 +17217,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -17343,7 +17343,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -17465,7 +17465,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17526,7 +17526,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17648,7 +17648,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17709,7 +17709,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17770,7 +17770,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17953,7 +17953,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18277,7 +18277,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -18327,7 +18327,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18388,7 +18388,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18647,7 +18647,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18823,7 +18823,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18884,7 +18884,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19189,7 +19189,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19372,7 +19372,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19555,7 +19555,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19738,7 +19738,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19921,7 +19921,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -20043,7 +20043,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20165,7 +20165,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20226,7 +20226,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20409,7 +20409,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20470,7 +20470,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20592,7 +20592,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20714,7 +20714,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20775,7 +20775,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20897,7 +20897,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20958,7 +20958,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -21019,7 +21019,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -21080,7 +21080,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
@@ -21145,7 +21145,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21206,7 +21206,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21267,7 +21267,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21389,7 +21389,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21572,7 +21572,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21755,7 +21755,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21770,7 +21770,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -22003,7 +22003,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22079,7 +22079,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
@@ -22129,7 +22129,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22190,7 +22190,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22205,7 +22205,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
@@ -22377,7 +22377,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22560,7 +22560,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22575,7 +22575,7 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -22625,7 +22625,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22686,7 +22686,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22808,7 +22808,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22930,7 +22930,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23113,7 +23113,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23235,7 +23235,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23296,7 +23296,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23357,7 +23357,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23418,7 +23418,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23479,7 +23479,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23601,7 +23601,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23662,7 +23662,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23723,7 +23723,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -23845,7 +23845,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -24028,7 +24028,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -24089,7 +24089,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -24272,7 +24272,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24333,7 +24333,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24455,7 +24455,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24531,7 +24531,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L393" t="inlineStr">
@@ -24581,7 +24581,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24642,7 +24642,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -25435,7 +25435,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25511,7 +25511,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -25698,7 +25698,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -26251,7 +26251,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L421" t="inlineStr">
@@ -26606,7 +26606,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26926,7 +26926,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -27281,7 +27281,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -28013,7 +28013,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -28379,7 +28379,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28867,7 +28867,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28928,7 +28928,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -29004,7 +29004,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L466" t="inlineStr">
@@ -29069,7 +29069,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -29119,7 +29119,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29302,7 +29302,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29378,7 +29378,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -29630,7 +29630,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L476" t="inlineStr">
@@ -30732,7 +30732,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
@@ -30797,7 +30797,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -30862,7 +30862,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L496" t="inlineStr">
@@ -30912,7 +30912,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L510" t="inlineStr">
@@ -31972,7 +31972,7 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L514" t="inlineStr">
@@ -32220,7 +32220,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L518" t="inlineStr">
@@ -32514,7 +32514,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32575,7 +32575,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32819,7 +32819,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -33063,7 +33063,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -33734,7 +33734,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33856,7 +33856,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33978,7 +33978,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -34039,7 +34039,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -34161,7 +34161,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34237,7 +34237,7 @@
       </c>
       <c r="K551" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L551" t="inlineStr">
@@ -35141,7 +35141,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35202,7 +35202,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35263,7 +35263,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -36971,7 +36971,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -37093,7 +37093,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -37520,7 +37520,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37825,7 +37825,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -38130,7 +38130,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38313,7 +38313,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38557,7 +38557,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38618,7 +38618,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -39167,7 +39167,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39350,7 +39350,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39777,7 +39777,7 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -39838,7 +39838,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -40509,7 +40509,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -41500,7 +41500,7 @@
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L670" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L671" t="inlineStr">
@@ -42225,7 +42225,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42347,7 +42347,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42713,7 +42713,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42774,7 +42774,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42896,7 +42896,7 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -42957,7 +42957,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -43018,7 +43018,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -43079,7 +43079,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43201,7 +43201,7 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43262,7 +43262,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43323,7 +43323,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43384,7 +43384,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43445,7 +43445,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43506,7 +43506,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43567,7 +43567,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43628,7 +43628,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43643,7 +43643,7 @@
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L705" t="inlineStr">
@@ -43693,7 +43693,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43754,7 +43754,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43815,7 +43815,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43876,7 +43876,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">

--- a/docs/oc-top-proveedores/adquisicion-de-vehiculos-y-maquinaria.xlsx
+++ b/docs/oc-top-proveedores/adquisicion-de-vehiculos-y-maquinaria.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -32709,7 +32709,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -39924,7 +39924,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
@@ -41094,7 +41094,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
@@ -41354,7 +41354,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -42849,7 +42849,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
@@ -43434,7 +43434,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
@@ -43564,7 +43564,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
@@ -43629,7 +43629,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
@@ -44929,7 +44929,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
